--- a/rules/CORE-001078/negative/01/data/unit-test-coreid-FB0609-negative.xlsx
+++ b/rules/CORE-001078/negative/01/data/unit-test-coreid-FB0609-negative.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-165" yWindow="-165" windowWidth="29130" windowHeight="15810" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Validation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="dm.xpt" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ae.xpt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Library" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dm.xpt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ae.xpt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,11 +63,6 @@
       <family val="2"/>
       <b val="1"/>
       <color rgb="FFFF0000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <sz val="11"/>
     </font>
     <font>
@@ -200,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -280,9 +275,6 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -290,28 +282,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -769,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.140625" bestFit="1" customWidth="1" min="5" max="5"/>
@@ -818,20 +794,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>8</v>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>USUBJID</t>
+          <t>$ae_fatal_death_count</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CDISC002</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -865,7 +843,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -899,7 +877,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ae.xpt</t>
+          <t>dm.xpt</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -908,160 +886,74 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USUBJID</t>
+          <t>DTHFL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CDISC003</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dm.xpt</t>
+          <t>ae.xpt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>7</v>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DTHFL</t>
+          <t>$ae_fatal_death_count</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ae.xpt</t>
+          <t>dm.xpt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>$ae_fatal_death_count</t>
+          <t>DTHFL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ae.xpt</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>12</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>USUBJID</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>CDISC004</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>dm.xpt</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>8</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>DTHFL</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
           <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ae.xpt</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>$ae_fatal_death_count</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1027,7 @@
           <t>DTHDTC</t>
         </is>
       </c>
-      <c r="L1" s="37" t="inlineStr">
+      <c r="L1" s="35" t="inlineStr">
         <is>
           <t>DTHFL</t>
         </is>
@@ -1963,7 +1855,7 @@
           <t>2018-12-11</t>
         </is>
       </c>
-      <c r="L8" s="40" t="inlineStr">
+      <c r="L8" s="36" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2185,7 +2077,7 @@
           <t>AESER</t>
         </is>
       </c>
-      <c r="F1" s="37" t="inlineStr">
+      <c r="F1" s="35" t="inlineStr">
         <is>
           <t>AEOUT</t>
         </is>
@@ -2483,7 +2375,7 @@
           <t>AE</t>
         </is>
       </c>
-      <c r="C8" s="41" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>CDISC002</t>
         </is>
@@ -2598,7 +2490,7 @@
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>CDISCPILOT01</t>
         </is>
@@ -2608,7 +2500,7 @@
           <t>AE</t>
         </is>
       </c>
-      <c r="C11" s="42" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>CDISC003</t>
         </is>
@@ -2618,7 +2510,7 @@
           <t>HEARING LOSS</t>
         </is>
       </c>
-      <c r="E11" s="33" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2639,10 +2531,10 @@
           <t>2006-06-20</t>
         </is>
       </c>
-      <c r="J11" s="34" t="n"/>
+      <c r="J11" s="33" t="n"/>
     </row>
     <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>CDISCPILOT01</t>
         </is>
@@ -2652,7 +2544,7 @@
           <t>AE</t>
         </is>
       </c>
-      <c r="C12" s="43" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>CDISC004</t>
         </is>
@@ -2662,17 +2554,17 @@
           <t>ACCIDENTAL OVERDOSE</t>
         </is>
       </c>
-      <c r="E12" s="33" t="inlineStr">
+      <c r="E12" s="32" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr">
-        <is>
-          <t>FATAL</t>
-        </is>
-      </c>
-      <c r="G12" s="36" t="n"/>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>RECOVERED/RESOLVED</t>
+        </is>
+      </c>
+      <c r="G12" s="34" t="n"/>
       <c r="H12" s="17" t="inlineStr">
         <is>
           <t>2018-12-11</t>
@@ -2683,7 +2575,7 @@
           <t>2018-12-11</t>
         </is>
       </c>
-      <c r="J12" s="34" t="n"/>
+      <c r="J12" s="33" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
